--- a/data/trans_orig/P25F_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023</t>
+          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023 (tasa de respuesta: 90,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>35423</t>
+          <t>34881</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>68785</t>
+          <t>68123</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>37770</t>
+          <t>39500</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>33702</t>
+          <t>33382</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>55247</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25F_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Clase-trans_orig.xlsx
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>658</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>741</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>979</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,27 +2576,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>27097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>14768</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29538</t>
+          <t>31179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>55391</t>
+          <t>66667</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>55391</t>
+          <t>66667</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>55391</t>
+          <t>66667</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>398</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>555</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>37199</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24406</t>
+          <t>28797</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>52286</t>
+          <t>55618</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>58195</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>34881</t>
+          <t>40482</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>68123</t>
+          <t>74990</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>39500</t>
+          <t>43417</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>23321</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>20793</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>32943</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>56435</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>96993</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>96993</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>96993</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>142446</t>
+          <t>162988</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>142446</t>
+          <t>162988</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>142446</t>
+          <t>162988</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
